--- a/documentacion_proyecto/Checklist_verificaciones.xlsx
+++ b/documentacion_proyecto/Checklist_verificaciones.xlsx
@@ -411,17 +411,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="IBM Plex Sans"/>
+      <name val="Arial"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="IBM Plex Sans"/>
+      <name val="Arial"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="IBM Plex Sans"/>
+      <name val="Arial"/>
       <family val="0"/>
     </font>
     <font>

--- a/documentacion_proyecto/Checklist_verificaciones.xlsx
+++ b/documentacion_proyecto/Checklist_verificaciones.xlsx
@@ -411,17 +411,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="IBM Plex Sans"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="IBM Plex Sans"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="IBM Plex Sans"/>
       <family val="0"/>
     </font>
     <font>
